--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-interpretation-code-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-interpretation-code-cs.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramInterpretationCode_VS</t>
   </si>
   <si>
     <t>Hierarchy</t>
@@ -388,45 +385,43 @@
       <c r="A16" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2"/>
     </row>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-interpretation-code-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-interpretation-code-cs.xlsx
@@ -23,7 +23,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramInterpretationCode_CS</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramInterpretationCode_CS</t>
   </si>
   <si>
     <t>Version</t>
